--- a/output/Sage_Leads_Batch01_2026-10-20.xlsx
+++ b/output/Sage_Leads_Batch01_2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Prospects" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Prospects'!$A$1:$R$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Prospects'!$A$1:$R$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,14 +427,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -442,7 +442,7 @@
     <col width="45" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Italian-Thai Development Public Company Limited "ITD"​</t>
+          <t>DTGO Group of Companies</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39900</v>
+        <v>4550</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -576,38 +576,38 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>itd.co.th</t>
+          <t>dtgo.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+66 2 716 1600</t>
+          <t>+66 2 088 6400</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/itdhq</t>
+          <t>http://www.linkedin.com/company/dtgocorporation</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>1958</v>
+        <v>1993</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>5ed8d44cc410b70001374c55</t>
+          <t>5fbba85534da7800f66ed576</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LINE MAN Wongnai</t>
+          <t>BUZZEBEES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18049.5</v>
+        <v>3570</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -638,38 +638,38 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>lmwn.com</t>
+          <t>buzzebees.com</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>+66 89 508 1168</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/line-man-wongnai</t>
+          <t>http://www.linkedin.com/company/buzzebees</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>LINE</t>
-        </is>
-      </c>
       <c r="N3" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>5fa91de479f99e00cacba90b</t>
+          <t>5fdc53c39f3c6f00015c2e89</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aCommerce</t>
+          <t>TD Tawandang Co.,Ltd.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9373.4</v>
+        <v>3500</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -700,38 +700,33 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>acommerce.asia</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>+66 2 261 3540</t>
+          <t>td tawandang co.,ltd.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/acommerce</t>
+          <t>http://www.linkedin.com/company/td-tawandang-co-ltd</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>54a1204d69702d94a4e21c02</t>
+          <t>5fc9ee273a075a00013bd770</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MFEC Public Company Limited</t>
+          <t>Aware Group</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -753,7 +748,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7620.3</v>
+        <v>3395</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -762,38 +757,38 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>mfec.co.th</t>
+          <t>aware.co.th</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+66 2 664 5999</t>
+          <t>+66 2 619 0226</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/mfec</t>
+          <t>http://www.linkedin.com/company/awaregroup</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>54a129ec69702dcef99de201</t>
+          <t>54a11e0869702da10ff64c01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>National ITMX Co., Ltd.</t>
+          <t>TEAM GROUP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -815,7 +810,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4585</v>
+        <v>1720.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -824,30 +819,38 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>itmx.co.th</t>
+          <t>teamgroup.co.th</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>+66 2 509 9000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/national-itmx</t>
+          <t>http://www.linkedin.com/company/teamgpcl</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="N6" t="n">
+        <v>1978</v>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5e55c2898a71b100016ede53</t>
+          <t>5e57ad678d755a0001a63b12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DTGO Group of Companies</t>
+          <t>Bluebik Group PLC.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,7 +872,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4550</v>
+        <v>1711</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -878,38 +881,38 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>dtgo.com</t>
+          <t>bluebik.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>+66 2 088 6400</t>
+          <t>+66 2 636 7011</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/dtgocorporation</t>
+          <t>http://www.linkedin.com/company/bluebikgroup</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.7</v>
+        <v>11.7</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1993</v>
+        <v>2013</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>5fbba85534da7800f66ed576</t>
+          <t>5e5618322e546f00019761ac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TD Tawandang Co.,Ltd.</t>
+          <t>Humanica Public Company Limited</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -931,7 +934,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3500</v>
+        <v>1684.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -940,33 +943,38 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>td tawandang co.,ltd.</t>
+          <t>humanica.com</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>+66 2 636 6999</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/td-tawandang-co-ltd</t>
+          <t>http://www.linkedin.com/company/humanicapcl</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.2</v>
+        <v>-2.8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2018</v>
+        <v>2003</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5fc9ee273a075a00013bd770</t>
+          <t>5e7ebdc69a840100c24a4411</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bluebik Group PLC.</t>
+          <t>Asphere Innovations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -988,7 +996,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1711</v>
+        <v>1351.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -997,31 +1005,31 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>bluebik.com</t>
+          <t>asphere.co</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+66 2 636 7011</t>
+          <t>+66 2 769 8888</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/bluebikgroup</t>
+          <t>http://www.linkedin.com/company/asphere-corporation-public-company-limited</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2013</v>
+        <v>2001</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5e5618322e546f00019761ac</t>
+          <t>5f8eb6332ad295008cbfc142</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1098,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dexon Technology</t>
+          <t>Beryl8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1112,47 +1120,47 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>910</v>
+        <v>1081.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>dexon-technology.com</t>
+          <t>beryl8.com</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+66330124847</t>
+          <t>+66 2 934 7427</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/dexon-technology</t>
+          <t>http://www.linkedin.com/company/beryl8-plus-company-limited</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1996</v>
+        <v>2009</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>5d33c1e8a3ae618995a8f3db</t>
+          <t>5d0a814580f93ef360cd0199</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRED IT Thailand</t>
+          <t>Bangkok Smartcard System Company Limited</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,47 +1182,47 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>868.2</v>
+        <v>1076.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>bred-it.com</t>
+          <t>rabbit.co.th</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+66 2 679 1070</t>
+          <t>+66 2 343 6493</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/bred-it-thailand</t>
+          <t>http://www.linkedin.com/company/bangkok-smartcard-system-company-limited</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>55923d8673696418f600eb00</t>
+          <t>55e88768f3e5bb353b000188</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G-ABLE Group</t>
+          <t>Dexon Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,7 +1244,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>824.7</v>
+        <v>910</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1245,38 +1253,38 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>g-able.com</t>
+          <t>dexon-technology.com</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+66 2 781 9000</t>
+          <t>+66330124847</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/gableth</t>
+          <t>http://www.linkedin.com/company/dexon-technology</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-0.2</v>
+        <v>-1.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1989</v>
+        <v>1996</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>60f793a75bb69f00013e33bd</t>
+          <t>5d33c1e8a3ae618995a8f3db</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amity Solutions</t>
+          <t>BRED IT Thailand</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1298,7 +1306,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>745.5</v>
+        <v>868.2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1307,33 +1315,38 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>amitysolutions.com</t>
+          <t>bred-it.com</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+66 2 679 1070</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/amity-solutions-hq</t>
+          <t>http://www.linkedin.com/company/bred-it-thailand</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>5fdb94b3a8c74700da9bb8bc</t>
+          <t>55923d8673696418f600eb00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>True Digital Group</t>
+          <t>I&amp;I Group PLC. - iiG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1355,7 +1368,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>383.9</v>
+        <v>840</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1364,43 +1377,38 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>truedigital.com</t>
+          <t>ii.co.th</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+66 2 021 0200</t>
+          <t>+66 2 248 3746</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/true-digital-group</t>
+          <t>http://www.linkedin.com/company/iandi-group</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>-3</v>
+        <v>1.1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>True Corporation</t>
-        </is>
-      </c>
       <c r="N15" t="n">
-        <v>1998</v>
+        <v>1991</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>5c215d80a3ae6181f76381b2</t>
+          <t>5a9eb2e0a6da98d938bc2807</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vinarco Group of Companies</t>
+          <t>G-ABLE Group</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1422,7 +1430,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>358.8</v>
+        <v>824.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1431,38 +1439,38 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>vinarco.com</t>
+          <t>g-able.com</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+66 2 649 2670</t>
+          <t>+66 2 781 9000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/vinarco-services-group-of-companies</t>
+          <t>http://www.linkedin.com/company/gableth</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>-5.7</v>
+        <v>-0.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1993</v>
+        <v>1989</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>54a135c969702d333d2f0601</t>
+          <t>60f793a75bb69f00013e33bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dwp.</t>
+          <t>Tractus</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,7 +1492,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>350</v>
+        <v>816.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1493,38 +1501,38 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>dwp.com</t>
+          <t>tractus-asia.com</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+66 2 267 3939</t>
+          <t>+1 651-262-7809</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/dwp-design-worldwide-partnership</t>
+          <t>http://www.linkedin.com/company/tractus-asia</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>-1.2</v>
+        <v>1.4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>54a1290f69702d9ebc224d01</t>
+          <t>54a1a7ad7468695c824e0705</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RECOFTC</t>
+          <t>Sirisoft Public Company Limited</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1546,7 +1554,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>322</v>
+        <v>778.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1555,33 +1563,38 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>recoftc.org</t>
+          <t>sirisoft.co.th</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>+66 2 006 5397</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/recoftc</t>
+          <t>http://www.linkedin.com/company/sirisoft-pcl</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>-6.9</v>
+        <v>-6.7</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1987</v>
+        <v>2015</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>54a1297769702db648349601</t>
+          <t>56e6c570f3e5bb3a2400a1f5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GreenTomatoMedia</t>
+          <t>Amity Solutions</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1603,7 +1616,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>280</v>
+        <v>745.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1612,38 +1625,33 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>greentomatomedia.com</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>+66 91 858 8546</t>
+          <t>amitysolutions.com</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/greentomatomedia</t>
+          <t>http://www.linkedin.com/company/amity-solutions-hq</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>-3.9</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>54a1209769702da425596302</t>
+          <t>5fdb94b3a8c74700da9bb8bc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Manatal</t>
+          <t>True Digital Group</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1665,7 +1673,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>210</v>
+        <v>383.9</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1674,38 +1682,43 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>manatal.com</t>
+          <t>truedigital.com</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+66 2 254 6681</t>
+          <t>+66 2 021 0200</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/manatal</t>
+          <t>http://www.linkedin.com/company/true-digital-group</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>15</v>
+        <v>-3</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>True Corporation</t>
+        </is>
+      </c>
       <c r="N20" t="n">
-        <v>2018</v>
+        <v>1998</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>5e55a3f7b721240001d185e6</t>
+          <t>5c215d80a3ae6181f76381b2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Plan B Media Public Company Limited</t>
+          <t>Vinarco Group of Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1715,11 +1728,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SaaS / Marketing Agency / Recruitment</t>
+          <t>IT / Management / Engineering Consulting</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1727,47 +1740,47 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10550.6</v>
+        <v>358.8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>planbmedia.co.th</t>
+          <t>vinarco.com</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+66 89 999 9199</t>
+          <t>+66 2 649 2670</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/plan-b-public-company-limited</t>
+          <t>http://www.linkedin.com/company/vinarco-services-group-of-companies</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2005</v>
+        <v>1993</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>57c4dc45a6da986a07d19c75</t>
+          <t>54a135c969702d333d2f0601</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jobsdb Thailand</t>
+          <t>dwp.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1777,11 +1790,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SaaS / Marketing Agency / Recruitment</t>
+          <t>IT / Management / Engineering Consulting</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1789,47 +1802,47 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5600</v>
+        <v>350</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>jobsdb.com</t>
+          <t>dwp.com</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>+66 2 267 3939</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/jobsdbthailand</t>
+          <t>http://www.linkedin.com/company/dwp-design-worldwide-partnership</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>-1.2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>SEEK</t>
-        </is>
-      </c>
       <c r="N22" t="n">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>5f44e4c22e43a00001ecac17</t>
+          <t>54a1290f69702d9ebc224d01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JD CENTRAL</t>
+          <t>TTCL Public Company Limited</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1839,11 +1852,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SaaS / Marketing Agency / Recruitment</t>
+          <t>IT / Management / Engineering Consulting</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1851,42 +1864,44 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5250</v>
+        <v>350</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>jd.co.th</t>
+          <t>ttcl.com</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>+66 2 260 8505</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/jdcentral</t>
+          <t>http://www.linkedin.com/company/ttcl-public-company-limited</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>2017</v>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>5b861aadf874f72e47be7851</t>
+          <t>55ea62a5f3e5bb02e0003631</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Omise</t>
+          <t>RECOFTC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1896,11 +1911,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SaaS / Marketing Agency / Recruitment</t>
+          <t>IT / Management / Engineering Consulting</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1908,52 +1923,42 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2422</v>
+        <v>322</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>omise.co</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>+66 2 252 8777</t>
+          <t>recoftc.org</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/omisepayments</t>
+          <t>http://www.linkedin.com/company/recoftc</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>7.5</v>
+        <v>-6.9</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Charoen Pokphand Group Co.,Ltd.</t>
-        </is>
-      </c>
       <c r="N24" t="n">
-        <v>2013</v>
+        <v>1987</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>54a120aa69702d9d7ea54202</t>
+          <t>54a1297769702db648349601</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>eatigo</t>
+          <t>GreenTomatoMedia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1963,11 +1968,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SaaS / Marketing Agency / Recruitment</t>
+          <t>IT / Management / Engineering Consulting</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1975,7 +1980,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1984,33 +1989,38 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>eatigo.com</t>
+          <t>greentomatomedia.com</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+66 91 858 8546</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/eatigo</t>
+          <t>http://www.linkedin.com/company/greentomatomedia</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>556e37517369641176e24e01</t>
+          <t>54a1209769702da425596302</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUO</t>
+          <t>Pronto Marketing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2020,11 +2030,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SaaS / Marketing Agency / Recruitment</t>
+          <t>IT / Management / Engineering Consulting</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2032,7 +2042,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>510.2</v>
+        <v>280</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2041,17 +2051,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>quo-global.com</t>
+          <t>prontomarketing.com</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+66 2 260 9494</t>
+          <t>+1 855-997-2731</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/quoglobal</t>
+          <t>http://www.linkedin.com/company/pronto-marketing</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2061,18 +2071,18 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>5f49ec7c4d6fbb0001179e09</t>
+          <t>54a12b0c69702d9b8b106a02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LTMH</t>
+          <t>Manatal</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2082,11 +2092,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SaaS / Marketing Agency / Recruitment</t>
+          <t>IT / Management / Engineering Consulting</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2094,7 +2104,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2103,47 +2113,52 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ltmh.com</t>
+          <t>manatal.com</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+66 2 254 6681</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/ltmhgroup</t>
+          <t>http://www.linkedin.com/company/manatal</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>-2.2</v>
+        <v>15</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>5e3d026de44326008cd1aded</t>
+          <t>5e55a3f7b721240001d185e6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>eatigo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Investment Holding / Private Equity / Venture Capital</t>
+          <t>SaaS / Marketing Agency / Recruitment</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2151,61 +2166,56 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2800</v>
+        <v>700</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>bitkub.com</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>+66 2 032 9555</t>
+          <t>eatigo.com</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/bitkub</t>
+          <t>http://www.linkedin.com/company/eatigo</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>-0.2</v>
+        <v>-3.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>5c207e2680f93e2412f78c34</t>
+          <t>556e37517369641176e24e01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>The Mall Group</t>
+          <t>QUO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Real Estate Investment / Asset Management</t>
+          <t>SaaS / Marketing Agency / Recruitment</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2213,56 +2223,61 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>70000</v>
+        <v>510.2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>themallgroup.com</t>
+          <t>quo-global.com</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+66 2 260 9494</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/the-mall-group</t>
+          <t>http://www.linkedin.com/company/quoglobal</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1981</v>
+        <v>1996</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>556d47247369641243e8d700</t>
+          <t>5f49ec7c4d6fbb0001179e09</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Siam Piwat</t>
+          <t>Rabbit's Tale</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Real Estate Investment / Asset Management</t>
+          <t>SaaS / Marketing Agency / Recruitment</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2270,61 +2285,66 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>53900</v>
+        <v>350</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>siampiwat.com</t>
+          <t>rabbitstale.com</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+66 2 658 1000</t>
+          <t>+66 2 219 2385</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/siam-piwat</t>
+          <t>http://www.linkedin.com/company/rabbitstale</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
       </c>
       <c r="N30" t="n">
-        <v>1959</v>
+        <v>2009</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>556dc9a373696411dec79301</t>
+          <t>5b84b349f874f7404ceef60f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AP (Thailand) Public Company Limited</t>
+          <t>LTMH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Real Estate Investment / Asset Management</t>
+          <t>SaaS / Marketing Agency / Recruitment</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2332,61 +2352,56 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>41350.9</v>
+        <v>280</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>apthai.com</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>+66 2 261 2518</t>
+          <t>ltmh.com</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/asian-property-development-public-co-ltd</t>
+          <t>http://www.linkedin.com/company/ltmhgroup</t>
         </is>
       </c>
       <c r="K31" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>240</v>
-      </c>
       <c r="N31" t="n">
-        <v>1991</v>
+        <v>2017</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>57c4f2e7a6da986aaa16d398</t>
+          <t>5e3d026de44326008cd1aded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BTS Group Holdings Public Company Limited</t>
+          <t>Kensington Associates Recruitment (Thailand) Ltd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Real Estate Investment / Asset Management</t>
+          <t>SaaS / Marketing Agency / Recruitment</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2394,47 +2409,47 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>24521.6</v>
+        <v>210</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>btsgroup.co.th</t>
+          <t>kensington.co.th</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>02-273-8611-15</t>
+          <t>026-348-8848</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/btsgroup2022</t>
+          <t>http://www.linkedin.com/company/kensington-associates-recruitment-thailand-ltd</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>-2.2</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>556948f27369642135852b00</t>
+          <t>54a1345d69702d31703e5200</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SC Asset Corporation PLC.</t>
+          <t>Bitkub</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2444,11 +2459,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Real Estate Investment / Asset Management</t>
+          <t>Investment Holding / Private Equity / Venture Capital</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2456,7 +2471,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22660.2</v>
+        <v>2800</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2465,38 +2480,38 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>scasset.com</t>
+          <t>bitkub.com</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+66 2 949 2000</t>
+          <t>+66 2 032 9555</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/scasset</t>
+          <t>http://www.linkedin.com/company/bitkub</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>7.6</v>
+        <v>-0.2</v>
       </c>
       <c r="L33" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>5d0ab1f7a3ae6198cbaceb50</t>
+          <t>5c207e2680f93e2412f78c34</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WHA Group</t>
+          <t>Asia Plus Group Holdings Public Company Limited</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2506,19 +2521,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Real Estate Investment / Asset Management</t>
+          <t>Investment Holding / Private Equity / Venture Capital</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NAICS</t>
+          <t>Name keyword</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>20195</v>
+        <v>2063.9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2527,38 +2542,38 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>wha-group.com</t>
+          <t>asiaplusgroup.co.th</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+66 2 680 1111</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/wha-corporation</t>
+          <t>http://www.linkedin.com/company/asiaplusgroup</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="L34" t="n">
-        <v>77</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>WHA Utilities and Power Public Company Limited</t>
-        </is>
+        <v>17</v>
       </c>
       <c r="N34" t="n">
-        <v>2003</v>
+        <v>1974</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>56d8b3b3f3e5bb57eb000062</t>
+          <t>5e57b78088fb670001ee7c37</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Frasers Property Industrial Thailand</t>
+          <t>Country Group Holdings Public Company Limited</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2568,19 +2583,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Real Estate Investment / Asset Management</t>
+          <t>Investment Holding / Private Equity / Venture Capital</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NAICS</t>
+          <t>Name keyword</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>15890</v>
+        <v>1557.6</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2589,43 +2604,38 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>frasersproperty.co.th</t>
+          <t>cgholdings.co.th</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>+66 2 483 0000</t>
+          <t>+66 2 256 7999</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/frasers-property-industrial-thailand</t>
+          <t>http://www.linkedin.com/company/country-group-holdings-public-company-limited</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>-2.3</v>
+        <v>45.5</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Frasers Property Limited</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="N35" t="n">
-        <v>1990</v>
+        <v>2015</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>623d42a1fcbec000c63a03ec</t>
+          <t>60b31b8651a12b00012a14e1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASSETWISE PLC</t>
+          <t>Pruksa Real Estate PLC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2647,7 +2657,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10216.1</v>
+        <v>13335</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2656,38 +2666,35 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>assetwise.co.th</t>
+          <t>pruksa.com</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+66 2 168 0000</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/assetwise-public-company-limited</t>
+          <t>http://www.linkedin.com/company/pruksa-real-estate-plc</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2005</v>
+        <v>112</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>63ccb7388d3e250001fdad61</t>
+          <t>559210e473696419815d4a00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Industrial Estate Authority Of Thailand (IEAT : กนอ.)</t>
+          <t>ASSETWISE PLC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2709,7 +2716,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9660</v>
+        <v>10216.1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2718,30 +2725,38 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ieat.go.th</t>
+          <t>assetwise.co.th</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>+66 2 168 0000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/industrial-estate-authority-of-thailand</t>
+          <t>http://www.linkedin.com/company/assetwise-public-company-limited</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L37" t="n">
-        <v>62</v>
+        <v>40</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2005</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>5e55c323090c4d0001f1390b</t>
+          <t>63ccb7388d3e250001fdad61</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Origin Property Public Company Limited.</t>
+          <t>Industrial Estate Authority Of Thailand (IEAT : กนอ.)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2763,7 +2778,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8915.4</v>
+        <v>9660</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2772,33 +2787,30 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>origin.co.th</t>
+          <t>ieat.go.th</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/origin-vertical-corporation-company-limited</t>
+          <t>http://www.linkedin.com/company/industrial-estate-authority-of-thailand</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>-3.1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>76</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2009</v>
+        <v>62</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>5c215a17a3ae61c528e5883f</t>
+          <t>5e55c323090c4d0001f1390b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Noble Development</t>
+          <t>Origin Property Public Company Limited.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2820,7 +2832,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>7673.2</v>
+        <v>8915.4</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2829,38 +2841,33 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>noblehome.com</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>+66 2 251 9955</t>
+          <t>origin.co.th</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/nobledevelopment</t>
+          <t>http://www.linkedin.com/company/origin-vertical-corporation-company-limited</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>-2</v>
+        <v>-3.1</v>
       </c>
       <c r="L39" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="N39" t="n">
-        <v>1991</v>
+        <v>2009</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>6048bb6eb7cda000019862e1</t>
+          <t>5c215a17a3ae61c528e5883f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LPN Development PCL.</t>
+          <t>Syntec Construction Public Company Limited</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2882,7 +2889,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>7455</v>
+        <v>8842.799999999999</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2891,38 +2898,38 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>lpn.co.th</t>
+          <t>synteccon.com</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>+66 2 285 5011</t>
+          <t>+66 2 026 2288</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/lpn-development-pcl</t>
+          <t>http://www.linkedin.com/company/syntec-construction-pcl</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>2.8</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>54a25eef7468693825f8e31d</t>
+          <t>5e580dbd3f9e640001a4bcf3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ananda Development Public Company Limited.</t>
+          <t>Noble Development</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2944,7 +2951,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7258</v>
+        <v>7673.2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2953,38 +2960,38 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ananda.co.th</t>
+          <t>noblehome.com</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+66 2 056 2222</t>
+          <t>+66 2 251 9955</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/ananda-development-plc-</t>
+          <t>http://www.linkedin.com/company/nobledevelopment</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>2.4</v>
+        <v>-2</v>
       </c>
       <c r="L41" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N41" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>57c4f63ca6da986a77cdc9ea</t>
+          <t>6048bb6eb7cda000019862e1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Siamese Asset Public Company Limited</t>
+          <t>LPN Development PCL.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3006,7 +3013,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2590.6</v>
+        <v>7455</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3015,33 +3022,38 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>siameseasset.co.th</t>
+          <t>lpn.co.th</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>+66 2 285 5011</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/siameseasset</t>
+          <t>http://www.linkedin.com/company/lpn-development-pcl</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="L42" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2010</v>
+        <v>1989</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>5ed19d687d32f60001564237</t>
+          <t>54a25eef7468693825f8e31d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Prinsiri</t>
+          <t>Ananda Development Public Company Limited.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3063,7 +3075,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1845.8</v>
+        <v>7258</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3072,38 +3084,38 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>prinsiri.com</t>
+          <t>ananda.co.th</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+66 2 617 6900</t>
+          <t>+66 2 056 2222</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/prinsiri</t>
+          <t>http://www.linkedin.com/company/ananda-development-plc-</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>-6.2</v>
+        <v>2.4</v>
       </c>
       <c r="L43" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N43" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>5da6fd05a8869b0001c8f18a</t>
+          <t>57c4f63ca6da986a77cdc9ea</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FazWaz</t>
+          <t>Lalin Property Public Company Limited (บริษัท ลลิล พร็อพเพอร์ตี้ จำกัด (มหาชน))</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3125,7 +3137,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1606.5</v>
+        <v>3248</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3134,43 +3146,38 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>fazwaz.com</t>
+          <t>lalinproperty.com</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>+66 2 508 8780</t>
+          <t>+66 2 732 1041</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/fazwaz</t>
+          <t>http://www.linkedin.com/company/%e0%b8%9a%e0%b8%a3%e0%b8%b4%e0%b8%a9%e0%b8%b1%e0%b8%97-%e0%b8%a5%e0%b8%a5%e0%b8%b4%e0%b8%a5-%e0%b8%9e%e0%b8%a3%e0%b9%87%e0%b8%ad%e0%b8%9e%e0%b9%80%e0%b8%9e%e0%b8%ad%e0%b8%a3%e0%b9%8c%e0%b8%95%e0%b8%b5%e0%b9%89-%e0%b8%88%e0%b8%b3%e0%b8%81%e0%b8%b1%e0%b8%94</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>8</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>FazWaz Property Group</t>
-        </is>
+        <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>2015</v>
+        <v>1988</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>5569bf497369642521278a00</t>
+          <t>5569c61a7369642529479100</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CBRE Thailand</t>
+          <t>Siamese Asset Public Company Limited</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3192,52 +3199,42 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>350</v>
+        <v>2590.6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>cbre.co.th</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>+66 2 119 2708</t>
+          <t>siameseasset.co.th</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/cbre-thailand</t>
+          <t>http://www.linkedin.com/company/siameseasset</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>CBRE</t>
-        </is>
+        <v>30</v>
       </c>
       <c r="N45" t="n">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>54a122b169702d918c48e702</t>
+          <t>5ed19d687d32f60001564237</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RML - Raimon Land PLC</t>
+          <t>Prinsiri</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3259,47 +3256,47 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>350</v>
+        <v>1845.8</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>raimonland.com</t>
+          <t>prinsiri.com</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+66 2 029 1888</t>
+          <t>+66 2 617 6900</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/raimon-land-plc</t>
+          <t>http://www.linkedin.com/company/prinsiri</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>6.8</v>
+        <v>-6.2</v>
       </c>
       <c r="L46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N46" t="n">
-        <v>1987</v>
+        <v>2000</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>54a12a5b69702dab379f2402</t>
+          <t>5da6fd05a8869b0001c8f18a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMATA</t>
+          <t>Sammakorn PLC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3321,47 +3318,47 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>212.4</v>
+        <v>1729.1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>amata.com</t>
+          <t>sammakorn.co.th</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>+1 212-586-5230</t>
+          <t>+66 2 106 8300</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/amatacorp</t>
+          <t>http://www.linkedin.com/company/sammakorn</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N47" t="n">
-        <v>1989</v>
+        <v>1974</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>5e56ed46913acc000105a4b3</t>
+          <t>60b06b7d79df5a00010cf128</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Knight Frank Thailand</t>
+          <t>FazWaz</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3383,58 +3380,66 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>203.5</v>
+        <v>1606.5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>knightfrank.co.th</t>
+          <t>fazwaz.com</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+66 2 643 8223</t>
+          <t>+66 2 508 8780</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/knight-frank-thailand</t>
+          <t>http://www.linkedin.com/company/fazwaz</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>FazWaz Property Group</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2015</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>6136d742812d0100015db9a2</t>
+          <t>5569bf497369642521278a00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>The Athenee Hotel, a Luxury Collection Hotel, Bangkok</t>
+          <t>KWI Public Company Limited</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3442,7 +3447,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>916510</v>
+        <v>1245.1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3451,52 +3456,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>marriott.com</t>
+          <t>kwiasia.com</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+65 6737 6888</t>
+          <t>+66 2 129 5999</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/theatheneehotel</t>
+          <t>http://www.linkedin.com/company/kwipcl</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>5b853d08324d440c9fbfbb4f</t>
+          <t>5569d1797369642585289d00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Central Pattana (CPN)</t>
+          <t>Bangkok Residence (BR)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3504,66 +3506,61 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>60411.4</v>
+        <v>385</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>centralpattana.co.th</t>
+          <t>thebkkresidence.com</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>+66 2 640 7000</t>
+          <t>+66 2 258 8189</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/centralpattana</t>
+          <t>http://www.linkedin.com/company/the-bangkok-residence</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>-0.4</v>
+        <v>6</v>
       </c>
       <c r="L50" t="n">
-        <v>113</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Central Group</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>1980</v>
+        <v>2009</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>5fbe1a6d0f4eef008ce5c7df</t>
+          <t>5a9da480a6da98d9663fe94c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sansiri PLC</t>
+          <t>MFC Asset Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3571,115 +3568,123 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>35375.9</v>
+        <v>361.9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>sansiri.com</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>+66 2 201 3999</t>
+          <t>mfcfund.com</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/sansiri-plc</t>
+          <t>http://www.linkedin.com/company/mfcfunds</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>-0.2</v>
+        <v>1.7</v>
       </c>
       <c r="L51" t="n">
-        <v>533</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>1984</v>
+        <v>1975</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>556dd10c73696411d5d6a101</t>
+          <t>5e56f9a61d824a00010d3bbf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Rosewood Bangkok</t>
+          <t>CBRE Thailand</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>350</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>cbre.co.th</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+66 2 119 2708</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/cbre-thailand</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L52" t="n">
         <v>2</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>NAICS</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>32994.5</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>rosewoodhotels.com</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>http://www.linkedin.com/company/rosewood-bangkok</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>CBRE</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1988</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>5c260ff580f93e2086f2f6f3</t>
+          <t>54a122b169702d918c48e702</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Centara Grand Lagoon Maldives</t>
+          <t>RML - Raimon Land PLC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3687,58 +3692,61 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>27685</v>
+        <v>350</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>centarahotelsresorts.com</t>
+          <t>raimonland.com</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+66 2 769 1234</t>
+          <t>+66 2 029 1888</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/centara-grand-lagoon-maldives</t>
+          <t>http://www.linkedin.com/company/raimon-land-plc</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>11.6</v>
+        <v>6.8</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1987</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>6718c9175791360001a27954</t>
+          <t>54a12a5b69702dab379f2402</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Asset World Corporation</t>
+          <t>Plus Property</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3746,61 +3754,58 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>21490</v>
+        <v>350</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>assetworldcorp-th.com</t>
+          <t>plus.co.th</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+66 2 180 9999</t>
+          <t>+66 2 688 7555</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/assetworldcorporation</t>
+          <t>http://www.linkedin.com/company/plus-property</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="L54" t="n">
-        <v>45</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1976</v>
+        <v>3</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>5e3ccf0263c4e100fcc68647</t>
+          <t>54a120e669702da4259c7d02</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SINGHA ESTATE PUBLIC COMPANY LIMITED</t>
+          <t>AMATA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3808,61 +3813,61 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>15648.3</v>
+        <v>212.4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>singhaestate.co.th</t>
+          <t>amata.com</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>+66 2 050 5555</t>
+          <t>+1 212-586-5230</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/singhaestate</t>
+          <t>http://www.linkedin.com/company/amatacorp</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="L55" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="N55" t="n">
-        <v>2014</v>
+        <v>1989</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>5da569b403ed82000124a597</t>
+          <t>5e56ed46913acc000105a4b3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MBK Public Company Limited</t>
+          <t>Siam Real Estate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3870,114 +3875,106 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>13409.2</v>
+        <v>210</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>mbkgroup.co.th</t>
+          <t>siamrealestate.com</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+66 2 853 9000</t>
+          <t>+66 76 383 646</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/mbk-public-company-limited</t>
+          <t>http://www.linkedin.com/company/siamrealestate</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>-3.9</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>1974</v>
+        <v>2003</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>5e55f859b0b5190001d2cc20</t>
+          <t>5d0a1329f6512560c7ee47a9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Centara Hotels &amp; Resorts</t>
+          <t>Knight Frank Thailand</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hotel &amp; Resort Groups</t>
+          <t>Real Estate Investment / Asset Management</t>
         </is>
       </c>
       <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>knightfrank.co.th</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>+66 2 643 8223</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/knight-frank-thailand</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
         <v>2</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>NAICS</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>11658.5</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>centara hotels &amp; resorts</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>+66 2 769 1234</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>http://www.linkedin.com/company/centara-hotels-&amp;-resorts</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L57" t="n">
-        <v>56</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Central Group</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
-        <v>1980</v>
-      </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>54a1395a69702d231fb46700</t>
+          <t>6136d742812d0100015db9a2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S Hotels &amp; Resorts Public Company Limited</t>
+          <t>The Athenee Hotel, a Luxury Collection Hotel, Bangkok</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3999,7 +3996,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10883.5</v>
+        <v>916510</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4008,38 +4005,38 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>shotelsresorts.com</t>
+          <t>marriott.com</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+66 2 058 9888</t>
+          <t>+65 6737 6888</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/s-hotels-resorts</t>
+          <t>http://www.linkedin.com/company/theatheneehotel</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>10.8</v>
+        <v>7.1</v>
       </c>
       <c r="L58" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>2014</v>
+        <v>2000</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>5edbbd2732600b000112dee0</t>
+          <t>5b853d08324d440c9fbfbb4f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dusit Hotels and Resorts</t>
+          <t>InterContinental Bangkok</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4061,7 +4058,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>10802.5</v>
+        <v>181615</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4070,43 +4067,38 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>dusit.com</t>
+          <t>ihg.com</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>+66 2 200 9999</t>
+          <t>+1 877-834-3613</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/dusit-hotels-and-resorts</t>
+          <t>http://www.linkedin.com/company/intercontinental-bangkok</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="L59" t="n">
-        <v>300</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Dusit International</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1949</v>
+        <v>2003</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>54a12a9769702d90a2f24f02</t>
+          <t>5cb33c77a3ae612b60e3ace7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dusit International</t>
+          <t>Central Pattana (CPN)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4128,7 +4120,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>9905</v>
+        <v>60411.4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4137,43 +4129,43 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>dusit-international.com</t>
+          <t>centralpattana.co.th</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+66 2 200 9999</t>
+          <t>+66 2 640 7000</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/dusitinternational</t>
+          <t>http://www.linkedin.com/company/centralpattana</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>-1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Dusit Hotels and Resorts</t>
+          <t>Central Group</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1948</v>
+        <v>1980</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>625cae164edc92014e98228c</t>
+          <t>5fbe1a6d0f4eef008ce5c7df</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>The Erawan Group Public Company Limited</t>
+          <t>Sansiri PLC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4195,7 +4187,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>8753.4</v>
+        <v>35375.9</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4204,38 +4196,38 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>theerawan.com</t>
+          <t>sansiri.com</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>+66 2 257 4588</t>
+          <t>+66 2 201 3999</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/erawan-group-pcl-the-erw-r-</t>
+          <t>http://www.linkedin.com/company/sansiri-plc</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="L61" t="n">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="N61" t="n">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>55e824daf3e5bb79c30009b5</t>
+          <t>556dd10c73696411d5d6a101</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Country Group Development PCL</t>
+          <t>Rosewood Bangkok</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4257,7 +4249,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3639.3</v>
+        <v>32994.5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4266,35 +4258,30 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>cgd.co.th</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>+66 2 658 7888</t>
+          <t>rosewoodhotels.com</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/country-group-development-public-company-limited</t>
+          <t>http://www.linkedin.com/company/rosewood-bangkok</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>57c48cc5a6da981595ea5495</t>
+          <t>5c260ff580f93e2086f2f6f3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Compass Hospitality</t>
+          <t>Centara Grand Lagoon Maldives</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4316,7 +4303,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1925</v>
+        <v>27685</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4325,38 +4312,35 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>compasshospitality.com</t>
+          <t>centarahotelsresorts.com</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>+66 2 168 7667</t>
+          <t>+66 2 769 1234</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/compasshospitality</t>
+          <t>http://www.linkedin.com/company/centara-grand-lagoon-maldives</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>8.300000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="L63" t="n">
-        <v>50</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1994</v>
+        <v>1</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>5f72f5c6ccbf0600bfbd1344</t>
+          <t>6718c9175791360001a27954</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ONYX Hospitality Group</t>
+          <t>Land and Houses PCL.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4378,47 +4362,47 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>525</v>
+        <v>22420.7</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>onyx-hospitality.com</t>
+          <t>lh.co.th</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>+66 2 653 9000</t>
+          <t>+1 408-707-1184</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/onyx-hospitality-group</t>
+          <t>http://www.linkedin.com/company/land-and-houses-pcl-lh-</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="L64" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="N64" t="n">
-        <v>2010</v>
+        <v>1973</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>54a1bed67468695c8282000d</t>
+          <t>55f709f0f3e5bb192c01f35c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Boutique Corporation Public Company Limited</t>
+          <t>Asset World Corporation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4440,47 +4424,47 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>461.6</v>
+        <v>21490</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>boutiquecorporation.com</t>
+          <t>assetworldcorp-th.com</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+66 2 620 8777</t>
+          <t>+66 2 180 9999</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/boutiquecorporationpcl</t>
+          <t>http://www.linkedin.com/company/assetworldcorporation</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>-1.8</v>
+        <v>1.4</v>
       </c>
       <c r="L65" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="N65" t="n">
-        <v>2007</v>
+        <v>1976</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>5e582d721e1aa1000133867f</t>
+          <t>5e3ccf0263c4e100fcc68647</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Six Senses</t>
+          <t>SINGHA ESTATE PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4502,52 +4486,47 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>455</v>
+        <v>15648.3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>sixsenses.com</t>
+          <t>singhaestate.co.th</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>+66 2 631 9777</t>
+          <t>+66 2 050 5555</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/six-senses-hotels-resorts</t>
+          <t>http://www.linkedin.com/company/singhaestate</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="L66" t="n">
-        <v>32</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Marriott</t>
-        </is>
+        <v>49</v>
       </c>
       <c r="N66" t="n">
-        <v>1995</v>
+        <v>2014</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>617f8c8f0fd512000183f947</t>
+          <t>5da569b403ed82000124a597</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Absolute Hotel Services</t>
+          <t>MBK Public Company Limited</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4569,47 +4548,47 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>455</v>
+        <v>13409.2</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>absolutehotelservices.net</t>
+          <t>mbkgroup.co.th</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>+66 2 255 9247</t>
+          <t>+66 2 853 9000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/absolute-hotel-services</t>
+          <t>http://www.linkedin.com/company/mbk-public-company-limited</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>6.7</v>
+        <v>-3.9</v>
       </c>
       <c r="L67" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="N67" t="n">
-        <v>2008</v>
+        <v>1974</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>61af3a913d335b011285816b</t>
+          <t>5e55f859b0b5190001d2cc20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IMPACT Exhibition and Convention Centre, Bangkok, Thailand</t>
+          <t>Centara Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4631,47 +4610,52 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>455</v>
+        <v>11658.5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>impact.co.th</t>
+          <t>centara hotels &amp; resorts</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>+66 2 833 4455</t>
+          <t>+66 2 769 1234</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/impact-exhibition-and-convention-centre-bangkok-thailand</t>
+          <t>http://www.linkedin.com/company/centara-hotels-&amp;-resorts</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>56</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Central Group</t>
+        </is>
       </c>
       <c r="N68" t="n">
-        <v>1999</v>
+        <v>1980</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>54a129b569702d931372d401</t>
+          <t>54a1395a69702d231fb46700</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kamalaya Koh Samui</t>
+          <t>S Hotels &amp; Resorts Public Company Limited</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4693,47 +4677,47 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>440.7</v>
+        <v>10883.5</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>kamalaya.com</t>
+          <t>shotelsresorts.com</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>+66 77 429 800</t>
+          <t>+66 2 058 9888</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/kamalayakohsamui</t>
+          <t>http://www.linkedin.com/company/s-hotels-resorts</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="N69" t="n">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>54a11d6569702da10fba0d01</t>
+          <t>5edbbd2732600b000112dee0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Chatrium Hospitality</t>
+          <t>Dusit Hotels and Resorts</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4755,47 +4739,52 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>385</v>
+        <v>10802.5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>chatrium.com</t>
+          <t>dusit.com</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>+66 2 307 8888</t>
+          <t>+66 2 200 9999</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/chatrium-hotels-&amp;-residences</t>
+          <t>http://www.linkedin.com/company/dusit-hotels-and-resorts</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="L70" t="n">
-        <v>9</v>
+        <v>300</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Dusit International</t>
+        </is>
       </c>
       <c r="N70" t="n">
-        <v>2008</v>
+        <v>1949</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>556941ec73696421587d2100</t>
+          <t>54a12a9769702d90a2f24f02</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lebua Hotels and Resorts</t>
+          <t>Dusit International</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4817,47 +4806,52 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>350</v>
+        <v>9905</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>lebua.com</t>
+          <t>dusit-international.com</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>+66 2 624 9999</t>
+          <t>+66 2 200 9999</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/lebua-hotels-and-resorts</t>
+          <t>http://www.linkedin.com/company/dusitinternational</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1.5</v>
+        <v>-1.1</v>
       </c>
       <c r="L71" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Dusit Hotels and Resorts</t>
+        </is>
       </c>
       <c r="N71" t="n">
-        <v>2003</v>
+        <v>1948</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>54a1ba7f74686949e728cf0b</t>
+          <t>625cae164edc92014e98228c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Chiva-Som International Health Resorts Co., Ltd.</t>
+          <t>The Erawan Group Public Company Limited</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4879,47 +4873,47 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>350</v>
+        <v>8753.4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>chivasom.com</t>
+          <t>theerawan.com</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>66-2711-6900-12</t>
+          <t>+66 2 257 4588</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/chiva-som</t>
+          <t>http://www.linkedin.com/company/erawan-group-pcl-the-erw-r-</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="N72" t="n">
-        <v>1993</v>
+        <v>1982</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>618cf47533975e0001256ec7</t>
+          <t>55e824daf3e5bb79c30009b5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GOCO Hospitality</t>
+          <t>Country Group Development PCL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4941,47 +4935,44 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>280</v>
+        <v>3639.3</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Core target (200M-1,000M)</t>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>gocohospitality.com</t>
+          <t>cgd.co.th</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>+66 2 252 6288</t>
+          <t>+66 2 658 7888</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/goco-hospitality</t>
+          <t>http://www.linkedin.com/company/country-group-development-public-company-limited</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>-3.7</v>
+        <v>2.2</v>
       </c>
       <c r="L73" t="n">
-        <v>6</v>
-      </c>
-      <c r="N73" t="n">
-        <v>2009</v>
+        <v>4</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>55699a227369642539b56800</t>
+          <t>57c48cc5a6da981595ea5495</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Central Restaurants Group</t>
+          <t>Compass Hospitality</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4991,11 +4982,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -5003,7 +4994,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>16170</v>
+        <v>1925</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5012,35 +5003,38 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>crg.co.th</t>
+          <t>compasshospitality.com</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>+66 2 635 7930</t>
+          <t>+66 2 168 7667</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/central-restaurants-group-co-ltd-</t>
+          <t>http://www.linkedin.com/company/compasshospitality</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1994</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>55f9b72ff3e5bb29f9000191</t>
+          <t>5f72f5c6ccbf0600bfbd1344</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S. Khonkaen Foods Public Company Ltd.</t>
+          <t>Sukosol Hotels</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5050,11 +5044,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -5062,42 +5056,47 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3891.8</v>
+        <v>941.1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>sorkon.co.th</t>
+          <t>sukosolhotels.com</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+66 2 247 0123</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/s-khonkaen-foods-public-company-ltd-</t>
+          <t>http://www.linkedin.com/company/sukosol-hotels</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>-9.800000000000001</v>
+        <v>-5.3</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N75" t="n">
-        <v>1984</v>
+        <v>1975</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>55e79d54f3e5bb3093000126</t>
+          <t>54a1223169702da425860703</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Freshket</t>
+          <t>Shama Lakeview Asoke</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5107,11 +5106,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -5119,47 +5118,39 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2527</v>
+        <v>902.6</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>freshket.co</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>+66 92 242 1495</t>
+          <t>shama.com</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/freshket-co</t>
+          <t>http://www.linkedin.com/company/shama-lakeview-asoke</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>-3.9</v>
+        <v>-7.7</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>2016</v>
+        <v>1</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>5e57eb89cecdff00017ff7a2</t>
+          <t>5f4a4c8f539afd0001195744</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>The Coffee Club (Thailand)</t>
+          <t>ONYX Hospitality Group</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5169,11 +5160,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -5181,7 +5172,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>805</v>
+        <v>525</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -5190,52 +5181,52 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>thecoffeeclub.co.th</t>
+          <t>onyx-hospitality.com</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>+61 7 4041 0522</t>
+          <t>+66 2 653 9000</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/the-coffee-club</t>
+          <t>http://www.linkedin.com/company/onyx-hospitality-group</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L77" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N77" t="n">
-        <v>1989</v>
+        <v>2010</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>615d071a4988af0001ec12fd</t>
+          <t>54a1bed67468695c8282000d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mae Fah Luang Foundation</t>
+          <t>The Absolute World Group</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Non-profit</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NGO / Foundation / Development Organisation</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -5243,58 +5234,56 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1085</v>
+        <v>525</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Large (1,000M+, compare with enterprise ERP)</t>
+          <t>Core target (200M-1,000M)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>maefahluang.org</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>+66 2 252 7114</t>
+          <t>absoluteworld.com</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/mae-fah-luang-foundation</t>
+          <t>http://www.linkedin.com/company/absolute-world</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1998</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>54a1361669702d407f74ff00</t>
+          <t>54a23eaa7468692e7108b119</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Asian Disaster Preparedness Center (ADPC)</t>
+          <t>Boutique Corporation Public Company Limited</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Non-profit</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NGO / Foundation / Development Organisation</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -5302,7 +5291,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>952.1</v>
+        <v>461.6</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5311,52 +5300,52 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>adpc.net</t>
+          <t>boutiquecorporation.com</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>+1 717-795-2000</t>
+          <t>+66 2 620 8777</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/asian-disaster-preparedness-center-adpc-</t>
+          <t>http://www.linkedin.com/company/boutiquecorporationpcl</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>11.1</v>
+        <v>-1.8</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N79" t="n">
-        <v>1986</v>
+        <v>2007</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>54a1231c69702d9a8b439b03</t>
+          <t>5e582d721e1aa1000133867f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Thailand Convention &amp; Exhibition Bureau (TCEB)</t>
+          <t>Six Senses</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Non-profit</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NGO / Foundation / Development Organisation</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -5364,7 +5353,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>350</v>
+        <v>455</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5373,52 +5362,57 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>tceb.or.th</t>
+          <t>sixsenses.com</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>+66 2 694 6000</t>
+          <t>+66 2 631 9777</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/businesseventsthailand</t>
+          <t>http://www.linkedin.com/company/six-senses-hotels-resorts</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
       </c>
       <c r="N80" t="n">
-        <v>2002</v>
+        <v>1995</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>5f46a3a2ec5ca70001c6093a</t>
+          <t>617f8c8f0fd512000183f947</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kenan Foundation Asia</t>
+          <t>Absolute Hotel Services</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Non-profit</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NGO / Foundation / Development Organisation</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -5426,7 +5420,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>292.3</v>
+        <v>455</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5435,52 +5429,52 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>kenan-asia.org</t>
+          <t>absolutehotelservices.net</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>+66 2 260 0380</t>
+          <t>+66 2 255 9247</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/kenan-asia</t>
+          <t>http://www.linkedin.com/company/absolute-hotel-services</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>-3.1</v>
+        <v>6.7</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N81" t="n">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>556994be7369642549f15d00</t>
+          <t>61af3a913d335b011285816b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ASEAN University Network</t>
+          <t>IMPACT Exhibition and Convention Centre, Bangkok, Thailand</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Non-profit</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NGO / Foundation / Development Organisation</t>
+          <t>Hotel &amp; Resort Groups</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -5488,7 +5482,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>245</v>
+        <v>455</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5497,93 +5491,1193 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>aunsec.org</t>
+          <t>impact.co.th</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>+66 2 215 3640</t>
+          <t>+66 2 833 4455</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/asean-university-network</t>
+          <t>http://www.linkedin.com/company/impact-exhibition-and-convention-centre-bangkok-thailand</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>10.4</v>
+        <v>0.7</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N82" t="n">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>5f41e78d60697d0001cb9bd2</t>
+          <t>54a129b569702d931372d401</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>Kamalaya Koh Samui</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hotel &amp; Resort Groups</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>440.7</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>kamalaya.com</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>+66 77 429 800</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/kamalayakohsamui</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2005</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>54a11d6569702da10fba0d01</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Chatrium Hospitality</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Hotel &amp; Resort Groups</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>385</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>chatrium.com</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>+66 2 307 8888</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/chatrium-hotels-&amp;-residences</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L84" t="n">
+        <v>9</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2008</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>556941ec73696421587d2100</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>lebua Hotels and Resorts</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hotel &amp; Resort Groups</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>350</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>lebua.com</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>+66 2 624 9999</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/lebua-hotels-and-resorts</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L85" t="n">
+        <v>18</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2003</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>54a1ba7f74686949e728cf0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Chiva-Som International Health Resorts Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Hotel &amp; Resort Groups</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>350</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>chivasom.com</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>66-2711-6900-12</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/chiva-som</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1993</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>618cf47533975e0001256ec7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sri panwa, Phuket</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Hotel &amp; Resort Groups</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>350</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>sripanwa.com</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>+66 76 371 000</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/sri-panwa-phuket</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>2005</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>54a11cac69702da4258dbc00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MSpa International</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Hotel &amp; Resort Groups</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>350</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>mspa-americas.org</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>+1 972-406-1104</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/mspa-international</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>25</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>5ed568a8e4829d0001723420</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GOCO Hospitality</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Hotel &amp; Resort Groups</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>280</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>gocohospitality.com</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>+66 2 252 6288</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/goco-hospitality</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="L89" t="n">
+        <v>6</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2009</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>55699a227369642539b56800</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Trisara Phuket</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Hotel &amp; Resort Groups</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>271.4</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>trisara.com</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>+66 76 310 100</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/trisara-phuket</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2005</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>556d6cb9736964123df90201</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Food Passion Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>foodpassion.co.th</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/foodpassion-people</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>270</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1987</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>640dc2d406d1c900a325d41a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S. Khonkaen Foods Public Company Ltd.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>3891.8</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>sorkon.co.th</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/s-khonkaen-foods-public-company-ltd-</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="L92" t="n">
+        <v>15</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1984</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>55e79d54f3e5bb3093000126</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Freshket</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>6</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2527</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>freshket.co</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>+66 92 242 1495</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/freshket-co</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>2016</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>5e57eb89cecdff00017ff7a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TANACHIRA Group</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>tanachira.co.th</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>+66 2 264 5081</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/tanachiragroup</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2010</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>5f895a3071b73100be00afcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>The Coffee Club (Thailand)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Restaurant Groups / Multi-outlet F&amp;B</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>6</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>805</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>thecoffeeclub.co.th</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>+61 7 4041 0522</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/the-coffee-club</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>45</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1989</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>615d071a4988af0001ec12fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Mae Fah Luang Foundation</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NGO / Foundation / Development Organisation</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1085</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Large (1,000M+, compare with enterprise ERP)</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>maefahluang.org</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>+66 2 252 7114</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/mae-fah-luang-foundation</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>54a1361669702d407f74ff00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Asian Disaster Preparedness Center (ADPC)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NGO / Foundation / Development Organisation</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>5</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>952.1</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>adpc.net</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>+1 717-795-2000</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/asian-disaster-preparedness-center-adpc-</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1986</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>54a1231c69702d9a8b439b03</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Thailand Convention &amp; Exhibition Bureau (TCEB)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NGO / Foundation / Development Organisation</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>5</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>350</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>tceb.or.th</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>+66 2 694 6000</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/businesseventsthailand</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>2002</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>5f46a3a2ec5ca70001c6093a</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Kenan Foundation Asia</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NGO / Foundation / Development Organisation</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>5</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>kenan-asia.org</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>+66 2 260 0380</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/kenan-asia</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1996</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>556994be7369642549f15d00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ASEAN University Network</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NGO / Foundation / Development Organisation</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>5</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>245</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Core target (200M-1,000M)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>aunsec.org</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>+66 2 215 3640</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/company/asean-university-network</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1995</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>5f41e78d60697d0001cb9bd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>APTN - Asia Pacific Transgender Network</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Non-profit</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>NGO / Foundation / Development Organisation</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D101" t="n">
         <v>5</v>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>NAICS</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>NAICS</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>200.7</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Core target (200M-1,000M)</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>weareaptn.org</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>http://www.linkedin.com/company/weareaptn</t>
         </is>
       </c>
-      <c r="K83" t="n">
+      <c r="K101" t="n">
         <v>-9.1</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L101" t="n">
         <v>0</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N101" t="n">
         <v>2009</v>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="R101" t="inlineStr">
         <is>
           <t>5e55f7d0524b29000117c065</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R83"/>
+  <autoFilter ref="A1:R101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>